--- a/data/trans_camb/IMC_inf_MED_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,95; 17,85</t>
+          <t>-22,47; 17,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 22,95</t>
+          <t>-25,2; 19,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 32,44</t>
+          <t>-6,63; 32,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-41,72; -5,75</t>
+          <t>-44,51; -5,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 19,95</t>
+          <t>-8,27; 20,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 0,1</t>
+          <t>-29,98; -0,51</t>
         </is>
       </c>
     </row>
@@ -707,39 +707,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,87; 55,8</t>
+          <t>-46,32; 54,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,62; 76,95</t>
+          <t>-53,45; 65,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 92,68</t>
+          <t>-10,75; 95,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-76,95; -14,14</t>
+          <t>-79,68; -13,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 53,14</t>
+          <t>-16,59; 58,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 1,02</t>
+          <t>-60,41; -1,02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 13,3</t>
+          <t>-11,27; 13,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 4,49</t>
+          <t>-40,63; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 15,77</t>
+          <t>-9,25; 16,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 14,41</t>
+          <t>-27,58; 9,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 11,31</t>
+          <t>-7,39; 11,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 0,25</t>
+          <t>-34,49; -1,64</t>
         </is>
       </c>
     </row>
@@ -863,39 +863,39 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 39,92</t>
+          <t>-23,96; 39,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-86,89; 11,34</t>
+          <t>-84,97; 15,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 35,21</t>
+          <t>-16,25; 37,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 32,16</t>
+          <t>-52,71; 21,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 26,33</t>
+          <t>-14,5; 28,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 0,44</t>
+          <t>-71,62; -3,83</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-40,0; -7,89</t>
+          <t>-39,27; -7,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-47,65; -10,32</t>
+          <t>-47,9; -7,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 2,49</t>
+          <t>-30,67; -0,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 18,63</t>
+          <t>-19,32; 18,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,38; -8,79</t>
+          <t>-30,88; -8,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,82; -0,91</t>
+          <t>-28,33; -0,89</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,57; -17,3</t>
+          <t>-63,13; -15,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,02; -20,18</t>
+          <t>-79,36; -16,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 5,37</t>
+          <t>-51,3; -0,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 40,99</t>
+          <t>-34,87; 39,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,13; -17,42</t>
+          <t>-52,79; -17,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,78; -1,71</t>
+          <t>-49,22; -1,56</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 16,8</t>
+          <t>-19,12; 16,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 9,03</t>
+          <t>-33,32; 10,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 10,12</t>
+          <t>-25,09; 10,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 32,88</t>
+          <t>-30,74; 30,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 8,36</t>
+          <t>-16,08; 8,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,81; 12,45</t>
+          <t>-25,55; 12,85</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 52,06</t>
+          <t>-41,21; 53,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-82,42; 31,11</t>
+          <t>-78,43; 38,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 19,89</t>
+          <t>-40,64; 23,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,64; 64,16</t>
+          <t>-54,83; 61,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 20,63</t>
+          <t>-31,42; 21,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,21; 29,45</t>
+          <t>-50,77; 29,45</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-39,93; 1,71</t>
+          <t>-40,73; -0,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 16,04</t>
+          <t>-27,57; 15,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 1,31</t>
+          <t>-38,03; 0,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 13,48</t>
+          <t>-28,12; 14,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,46; -5,45</t>
+          <t>-33,71; -4,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 9,56</t>
+          <t>-22,95; 8,51</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,91; 5,9</t>
+          <t>-69,53; -0,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,1; 45,47</t>
+          <t>-47,21; 43,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 2,36</t>
+          <t>-58,2; 1,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-42,35; 29,5</t>
+          <t>-42,67; 32,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-59,04; -12,81</t>
+          <t>-56,88; -9,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 21,58</t>
+          <t>-38,06; 18,09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 5,27</t>
+          <t>-29,34; 3,15</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-45,15; -5,69</t>
+          <t>-42,79; -4,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 27,84</t>
+          <t>-9,85; 27,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 14,12</t>
+          <t>-27,05; 16,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 10,2</t>
+          <t>-14,33; 10,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-27,21; -0,8</t>
+          <t>-26,92; 1,1</t>
         </is>
       </c>
     </row>
@@ -1487,39 +1487,39 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 15,99</t>
+          <t>-57,99; 9,78</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-90,71; -14,02</t>
+          <t>-89,79; -9,94</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 93,86</t>
+          <t>-21,29; 94,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 43,85</t>
+          <t>-58,44; 51,94</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 29,1</t>
+          <t>-29,51; 28,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-60,43; -1,81</t>
+          <t>-60,04; 2,9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-25,11; -3,5</t>
+          <t>-26,03; -3,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 12,65</t>
+          <t>-17,76; 12,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-34,52; -11,66</t>
+          <t>-34,26; -11,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 0,16</t>
+          <t>-26,52; 1,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-26,69; -11,07</t>
+          <t>-26,57; -10,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 3,19</t>
+          <t>-16,85; 3,28</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-55,54; -9,72</t>
+          <t>-57,48; -9,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 36,36</t>
+          <t>-41,2; 34,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,13; -22,58</t>
+          <t>-54,38; -22,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 0,71</t>
+          <t>-41,96; 3,45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,6; -23,73</t>
+          <t>-50,07; -22,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,95; 6,73</t>
+          <t>-32,49; 7,14</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -1,14</t>
+          <t>-20,2; 0,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-42,23; -16,96</t>
+          <t>-40,78; -16,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 2,19</t>
+          <t>-18,83; 1,26</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-30,45; -6,51</t>
+          <t>-30,76; -4,96</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-16,39; -1,62</t>
+          <t>-17,24; -2,3</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-31,14; -13,48</t>
+          <t>-31,62; -13,53</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-36,19; -2,1</t>
+          <t>-35,95; -0,05</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-76,41; -35,33</t>
+          <t>-75,15; -35,86</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 4,85</t>
+          <t>-30,14; 2,28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-50,47; -12,4</t>
+          <t>-50,47; -9,79</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-28,67; -3,42</t>
+          <t>-29,38; -4,38</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,84; -25,97</t>
+          <t>-54,37; -25,47</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -5,42</t>
+          <t>-15,21; -5,1</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-27,4; -10,3</t>
+          <t>-25,83; -9,64</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -3,08</t>
+          <t>-13,17; -3,12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -6,51</t>
+          <t>-18,72; -5,93</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-12,74; -5,54</t>
+          <t>-12,62; -5,21</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-20,54; -9,67</t>
+          <t>-19,41; -9,09</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -12,81</t>
+          <t>-32,32; -12,23</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-60,09; -23,86</t>
+          <t>-56,28; -22,13</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-23,46; -6,07</t>
+          <t>-23,62; -6,22</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-33,79; -12,35</t>
+          <t>-33,57; -11,34</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-25,12; -11,73</t>
+          <t>-24,67; -10,96</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-41,25; -20,06</t>
+          <t>-39,11; -18,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Provincia-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 17,22</t>
+          <t>-22,46; 17,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 19,81</t>
+          <t>-25,82; 21,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 32,94</t>
+          <t>-8,2; 34,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,51; -5,41</t>
+          <t>-43,14; -4,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 20,33</t>
+          <t>-9,98; 19,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,98; -0,51</t>
+          <t>-30,29; 0,47</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,32; 54,62</t>
+          <t>-43,58; 54,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 65,13</t>
+          <t>-53,45; 70,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 95,59</t>
+          <t>-15,27; 103,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-79,68; -13,88</t>
+          <t>-77,08; -8,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 58,05</t>
+          <t>-20,87; 54,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,41; -1,02</t>
+          <t>-60,24; 4,71</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 13,6</t>
+          <t>-12,68; 13,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 5,52</t>
+          <t>-40,4; 4,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 16,28</t>
+          <t>-8,94; 16,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,58; 9,21</t>
+          <t>-26,79; 10,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 11,99</t>
+          <t>-7,33; 10,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,49; -1,64</t>
+          <t>-35,34; -0,17</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 39,69</t>
+          <t>-28,13; 38,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-84,97; 15,36</t>
+          <t>-85,76; 14,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 37,36</t>
+          <t>-15,39; 39,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,71; 21,04</t>
+          <t>-50,23; 24,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 28,56</t>
+          <t>-14,8; 26,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,62; -3,83</t>
+          <t>-73,16; -0,33</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-39,27; -7,47</t>
+          <t>-40,51; -8,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-47,9; -7,49</t>
+          <t>-47,25; -12,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,67; -0,12</t>
+          <t>-30,69; 0,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 18,59</t>
+          <t>-18,95; 18,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,88; -8,66</t>
+          <t>-31,25; -8,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,33; -0,89</t>
+          <t>-28,13; -0,1</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,13; -15,86</t>
+          <t>-64,35; -17,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,36; -16,33</t>
+          <t>-79,22; -25,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -0,31</t>
+          <t>-51,11; 3,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,87; 39,23</t>
+          <t>-32,95; 41,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,79; -17,65</t>
+          <t>-51,47; -17,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,22; -1,56</t>
+          <t>-49,5; -0,15</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 16,88</t>
+          <t>-20,4; 15,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 10,73</t>
+          <t>-34,99; 9,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 10,94</t>
+          <t>-23,32; 9,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 30,86</t>
+          <t>-23,97; 35,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 8,56</t>
+          <t>-15,95; 8,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 12,85</t>
+          <t>-25,59; 11,86</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 53,52</t>
+          <t>-42,57; 48,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,43; 38,36</t>
+          <t>-79,07; 31,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,64; 23,59</t>
+          <t>-39,41; 19,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 61,38</t>
+          <t>-42,82; 73,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 21,15</t>
+          <t>-30,57; 21,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 29,45</t>
+          <t>-50,22; 25,63</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-40,73; -0,2</t>
+          <t>-41,12; 2,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 15,9</t>
+          <t>-27,72; 18,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 0,43</t>
+          <t>-41,09; 0,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 14,35</t>
+          <t>-28,41; 16,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,71; -4,75</t>
+          <t>-34,5; -3,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 8,51</t>
+          <t>-21,48; 9,25</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,53; -0,35</t>
+          <t>-68,51; 9,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 43,43</t>
+          <t>-45,7; 54,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 1,0</t>
+          <t>-62,48; 2,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 32,24</t>
+          <t>-44,04; 37,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,88; -9,99</t>
+          <t>-56,97; -8,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 18,09</t>
+          <t>-35,39; 21,62</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 3,15</t>
+          <t>-30,29; 5,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-42,79; -4,16</t>
+          <t>-44,47; -7,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 27,64</t>
+          <t>-7,16; 26,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 16,6</t>
+          <t>-25,85; 15,64</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 10,01</t>
+          <t>-13,24; 10,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 1,1</t>
+          <t>-27,15; 0,99</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 9,78</t>
+          <t>-59,14; 15,54</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-89,79; -9,94</t>
+          <t>-90,53; -18,78</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 94,35</t>
+          <t>-16,67; 89,61</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 51,94</t>
+          <t>-58,05; 50,92</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-29,51; 28,43</t>
+          <t>-28,16; 29,22</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 2,9</t>
+          <t>-59,28; 2,75</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-26,03; -3,34</t>
+          <t>-25,33; -4,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 12,81</t>
+          <t>-17,27; 13,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-34,26; -11,33</t>
+          <t>-35,47; -13,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-26,52; 1,7</t>
+          <t>-25,74; 1,3</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-26,57; -10,36</t>
+          <t>-26,64; -10,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 3,28</t>
+          <t>-17,21; 2,76</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-57,48; -9,18</t>
+          <t>-55,54; -11,36</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,2; 34,97</t>
+          <t>-40,7; 37,77</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,38; -22,58</t>
+          <t>-55,22; -24,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 3,45</t>
+          <t>-42,27; 1,7</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,07; -22,58</t>
+          <t>-50,06; -22,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 7,14</t>
+          <t>-33,22; 6,52</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 0,06</t>
+          <t>-20,6; 0,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-40,78; -16,41</t>
+          <t>-41,73; -17,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 1,26</t>
+          <t>-18,23; 1,72</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-30,76; -4,96</t>
+          <t>-31,4; -4,75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,24; -2,3</t>
+          <t>-16,77; -2,46</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-31,62; -13,53</t>
+          <t>-31,54; -14,21</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-35,95; -0,05</t>
+          <t>-37,33; -0,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-75,15; -35,86</t>
+          <t>-75,3; -37,33</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-30,14; 2,28</t>
+          <t>-29,35; 3,28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-50,47; -9,79</t>
+          <t>-50,24; -8,93</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-29,38; -4,38</t>
+          <t>-29,04; -5,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,37; -25,47</t>
+          <t>-54,99; -26,46</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -5,1</t>
+          <t>-15,64; -5,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-25,83; -9,64</t>
+          <t>-25,94; -10,11</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -3,12</t>
+          <t>-12,95; -2,37</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-18,72; -5,93</t>
+          <t>-19,57; -5,75</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-12,62; -5,21</t>
+          <t>-12,47; -5,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-19,41; -9,09</t>
+          <t>-20,57; -9,61</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -12,23</t>
+          <t>-32,68; -12,41</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-56,28; -22,13</t>
+          <t>-56,06; -23,2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-23,62; -6,22</t>
+          <t>-23,08; -4,45</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-33,57; -11,34</t>
+          <t>-35,04; -10,95</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -10,96</t>
+          <t>-24,67; -11,26</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-39,11; -18,97</t>
+          <t>-40,7; -19,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-24,12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-2,29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-5,12</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14,01</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-24,47</t>
+          <t>-10,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-15,82</t>
+          <t>-17,63</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 17,45</t>
+          <t>-7,37; 32,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 21,2</t>
+          <t>-41,69; -6,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 34,83</t>
+          <t>-19,95; 17,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-43,14; -4,27</t>
+          <t>-29,15; 10,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 19,55</t>
+          <t>-9,17; 19,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 0,47</t>
+          <t>-31,34; -3,67</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30,38%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-52,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-5,52%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-12,34%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30,38%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-53,04%</t>
+          <t>-24,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-36,0%</t>
+          <t>-40,12%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,58; 54,76</t>
+          <t>-13,18; 92,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 70,81</t>
+          <t>-75,3; -11,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 103,11</t>
+          <t>-41,87; 55,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,08; -8,71</t>
+          <t>-59,36; 38,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 54,54</t>
+          <t>-18,35; 53,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,24; 4,71</t>
+          <t>-62,14; -9,19</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-11,51</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-18,14</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-10,94</t>
+          <t>-9,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-16,11</t>
+          <t>-10,49</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 13,51</t>
+          <t>-10,28; 15,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 4,91</t>
+          <t>-28,02; 12,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 16,92</t>
+          <t>-11,39; 13,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 10,74</t>
+          <t>-25,48; 8,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 10,66</t>
+          <t>-7,79; 11,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,34; -0,17</t>
+          <t>-22,74; 3,66</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-22,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-44,44%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-21,72%</t>
+          <t>-22,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-35,17%</t>
+          <t>-22,9%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 38,93</t>
+          <t>-18,32; 35,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,76; 14,34</t>
+          <t>-52,32; 29,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 39,13</t>
+          <t>-25,18; 39,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,23; 24,97</t>
+          <t>-55,73; 24,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 26,04</t>
+          <t>-15,38; 26,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,16; -0,33</t>
+          <t>-45,96; 10,17</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-15,37</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,11</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-23,64</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-30,81</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-15,37</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-30,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-14,67</t>
+          <t>-14,97</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-40,51; -8,28</t>
+          <t>-30,52; 2,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-47,25; -12,49</t>
+          <t>-20,47; 19,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 0,49</t>
+          <t>-40,0; -7,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 18,87</t>
+          <t>-46,96; -9,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,25; -8,34</t>
+          <t>-31,38; -8,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,13; -0,1</t>
+          <t>-28,68; -0,75</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-29,3%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-0,2%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-42,71%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-55,67%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-29,3%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,78%</t>
+          <t>-54,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,23%</t>
+          <t>-27,79%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,35; -17,02</t>
+          <t>-50,93; 5,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,22; -25,18</t>
+          <t>-35,41; 40,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 3,57</t>
+          <t>-62,57; -17,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,95; 41,07</t>
+          <t>-77,46; -19,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,47; -17,47</t>
+          <t>-52,13; -17,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,5; -0,15</t>
+          <t>-49,0; -1,4</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-7,26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,02</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,99</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-15,5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,26</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>-15,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,96</t>
+          <t>-9,15</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 15,11</t>
+          <t>-24,57; 10,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 9,5</t>
+          <t>-32,9; 32,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 9,26</t>
+          <t>-17,51; 16,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 35,61</t>
+          <t>-35,41; 8,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 8,86</t>
+          <t>-16,67; 8,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 11,86</t>
+          <t>-28,27; 11,49</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-13,14%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-2,56%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-39,93%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-13,14%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>-39,08%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-16,79%</t>
+          <t>-19,3%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 48,61</t>
+          <t>-40,67; 19,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-79,07; 31,16</t>
+          <t>-56,39; 63,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 19,38</t>
+          <t>-39,76; 52,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 73,08</t>
+          <t>-83,6; 30,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 21,88</t>
+          <t>-32,32; 20,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 25,63</t>
+          <t>-55,61; 26,77</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-19,49</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-6,36</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-20,38</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-5,55</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-19,49</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-6,64</t>
+          <t>-5,98</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-6,13</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-41,12; 2,67</t>
+          <t>-41,18; 1,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 18,03</t>
+          <t>-26,95; 13,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 0,81</t>
+          <t>-39,93; 1,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 16,85</t>
+          <t>-27,91; 16,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-34,5; -3,92</t>
+          <t>-35,46; -5,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 9,25</t>
+          <t>-21,59; 9,51</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-34,6%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-11,29%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-41,76%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-11,38%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-34,6%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-11,8%</t>
+          <t>-12,26%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-11,46%</t>
+          <t>-11,61%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 9,19</t>
+          <t>-62,03; 2,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 54,52</t>
+          <t>-42,23; 30,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,48; 2,1</t>
+          <t>-67,91; 5,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 37,36</t>
+          <t>-46,14; 44,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,97; -8,59</t>
+          <t>-59,04; -12,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,39; 21,62</t>
+          <t>-35,16; 21,68</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>9,38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-5,97</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-12,86</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-27,53</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>9,38</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-4,71</t>
+          <t>-27,7</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-13,98</t>
+          <t>-15,39</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 5,07</t>
+          <t>-6,63; 27,84</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-44,47; -7,75</t>
+          <t>-25,66; 12,91</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 26,5</t>
+          <t>-29,08; 5,27</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 15,64</t>
+          <t>-45,74; -6,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 10,14</t>
+          <t>-13,82; 10,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 0,99</t>
+          <t>-28,01; -2,26</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>23,95%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-15,23%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-29,55%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-63,28%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>23,95%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-12,03%</t>
+          <t>-63,67%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-33,77%</t>
+          <t>-37,17%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-59,14; 15,54</t>
+          <t>-15,88; 93,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-90,53; -18,78</t>
+          <t>-52,8; 37,88</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 89,61</t>
+          <t>-58,58; 15,99</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-58,05; 50,92</t>
+          <t>-90,82; -12,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 29,22</t>
+          <t>-29,5; 29,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-59,28; 2,75</t>
+          <t>-62,86; -5,72</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-23,48</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-13,14</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-14,4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-3,43</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-23,48</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-12,66</t>
+          <t>-7,3</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-7,21</t>
+          <t>-9,16</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-25,33; -4,3</t>
+          <t>-34,52; -11,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 13,2</t>
+          <t>-26,17; -0,03</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-35,47; -13,13</t>
+          <t>-25,11; -3,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 1,3</t>
+          <t>-20,11; 7,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-26,64; -10,52</t>
+          <t>-26,69; -11,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 2,76</t>
+          <t>-18,84; 1,2</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-40,19%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-22,49%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-36,27%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-8,63%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-40,19%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-21,66%</t>
+          <t>-18,39%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-14,68%</t>
+          <t>-18,67%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-55,54; -11,36</t>
+          <t>-55,13; -22,58</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,7; 37,77</t>
+          <t>-42,36; -0,07</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,22; -24,12</t>
+          <t>-55,54; -9,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 1,7</t>
+          <t>-47,81; 22,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,06; -22,57</t>
+          <t>-50,6; -23,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 6,52</t>
+          <t>-36,34; 2,22</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-8,66</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-19,28</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-10,73</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>-30,08</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-8,66</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-18,84</t>
+          <t>-31,3</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-22,54</t>
+          <t>-23,38</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 0,3</t>
+          <t>-18,06; 2,19</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-41,73; -17,78</t>
+          <t>-31,24; -6,9</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 1,72</t>
+          <t>-20,55; -1,14</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-31,4; -4,75</t>
+          <t>-43,28; -18,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-16,77; -2,46</t>
+          <t>-16,39; -1,62</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-31,54; -14,21</t>
+          <t>-31,83; -14,4</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-14,87%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-33,1%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-20,87%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>-58,52%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-14,87%</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-32,35%</t>
+          <t>-60,9%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-41,08%</t>
+          <t>-42,61%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-37,33; -0,36</t>
+          <t>-28,44; 4,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-75,3; -37,33</t>
+          <t>-51,66; -12,31</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 3,28</t>
+          <t>-36,19; -2,1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-50,24; -8,93</t>
+          <t>-77,91; -37,59</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-29,04; -5,0</t>
+          <t>-28,67; -3,42</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-54,99; -26,46</t>
+          <t>-56,06; -27,79</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-8,33</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-12,6</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-10,25</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>-17,3</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-8,33</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-12,64</t>
+          <t>-17,07</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-14,48</t>
+          <t>-14,2</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -5,22</t>
+          <t>-13,25; -3,08</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-25,94; -10,11</t>
+          <t>-18,77; -6,64</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -2,37</t>
+          <t>-15,41; -5,42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-19,57; -5,75</t>
+          <t>-22,85; -10,41</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-12,47; -5,26</t>
+          <t>-12,74; -5,54</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-20,57; -9,61</t>
+          <t>-18,7; -9,74</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-15,51%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-23,47%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-22,77%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>-38,41%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-15,51%</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-23,54%</t>
+          <t>-37,89%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-29,27%</t>
+          <t>-28,71%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -12,41</t>
+          <t>-23,46; -6,07</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-56,06; -23,2</t>
+          <t>-33,86; -12,81</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-23,08; -4,45</t>
+          <t>-32,92; -12,81</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -10,95</t>
+          <t>-49,05; -24,42</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -11,26</t>
+          <t>-25,12; -11,73</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-40,7; -19,83</t>
+          <t>-36,97; -20,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Provincia-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>14.01256101219274</v>
+        <v>3.157290758642922</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-24.11776831559861</v>
+        <v>-25.21934355146206</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-2.290960537011599</v>
+        <v>-8.72284437114217</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-10.18079156279499</v>
+        <v>-12.2917795777976</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>5.547588382133995</v>
+        <v>-2.572277179680599</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-17.63232459313754</v>
+        <v>-19.23919452656257</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-7.372984777302119</v>
+        <v>-12.32555355837639</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-41.6851691865573</v>
+        <v>-41.47900024590435</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-19.94589244216332</v>
+        <v>-23.83515737895361</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-29.15190541171955</v>
+        <v>-29.81784214352279</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-9.16576330071555</v>
+        <v>-14.41982091046538</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-31.33993457264599</v>
+        <v>-31.93453495848998</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>32.43717239700351</v>
+        <v>19.34636170211439</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-6.266979604284235</v>
+        <v>-7.613379483856162</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>17.85457679662761</v>
+        <v>8.115114010460971</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>10.85822477885504</v>
+        <v>6.516688546570956</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>19.9535223523852</v>
+        <v>8.445520015221121</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-3.670690974700288</v>
+        <v>-6.372170950660386</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.303775930094322</v>
+        <v>0.06684993595420764</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.5228450028153616</v>
+        <v>-0.5339741031475487</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.05520286138057354</v>
+        <v>-0.20001135849915</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.2453158037015279</v>
+        <v>-0.2818456259360605</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.1262128593609561</v>
+        <v>-0.05645775632900021</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.4011519872756565</v>
+        <v>-0.4222724382610192</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.1317699776731126</v>
+        <v>-0.2301951246323518</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.7530117335363006</v>
+        <v>-0.7605737590305544</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.4186667920040632</v>
+        <v>-0.46437771721476</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.5935865329385148</v>
+        <v>-0.6025280400535968</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.183451788202156</v>
+        <v>-0.2860139654254574</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.621380310694496</v>
+        <v>-0.6202866722038487</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.9267636145715659</v>
+        <v>0.522577139033962</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-0.1172510855892193</v>
+        <v>-0.1634165542994689</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.5580242775974594</v>
+        <v>0.2414103071921657</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3813416575016189</v>
+        <v>0.1905489523227971</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.5313945635321051</v>
+        <v>0.2176127523577852</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.09193906001726665</v>
+        <v>-0.1469356474404617</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3.463253479914186</v>
+        <v>0.6948812387903902</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-11.50691595743243</v>
+        <v>-11.12578635798263</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.8944090455716203</v>
+        <v>0.5667674699450398</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-9.37956617180043</v>
+        <v>-11.78268693173409</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>2.03351651707715</v>
+        <v>0.6527800485360946</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-10.48845537486823</v>
+        <v>-11.40200817692229</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-10.27760913370828</v>
+        <v>-11.41709997873605</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-28.01856950165422</v>
+        <v>-27.80557885410961</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-11.38827938105018</v>
+        <v>-12.12337008362805</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-25.47613026488001</v>
+        <v>-26.62524632061153</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-7.787524031316052</v>
+        <v>-8.130603966936425</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-22.73643257074195</v>
+        <v>-22.84310771307208</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>15.77444419630034</v>
+        <v>11.32703970761311</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>12.90056863838042</v>
+        <v>8.614142914095286</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>13.30249729335312</v>
+        <v>11.85642075823057</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>8.376607039339941</v>
+        <v>4.404694386760209</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>11.30941371027228</v>
+        <v>9.512612138793472</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>3.664132882150726</v>
+        <v>2.435427435362745</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0.06876659015215979</v>
+        <v>0.01415216373216653</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.2284820843029112</v>
+        <v>-0.2265911660838072</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.0219186892050305</v>
+        <v>0.0131169170733518</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.2298588065668761</v>
+        <v>-0.2726912456704849</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.04439453970371781</v>
+        <v>0.0141003403529601</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.2289778050288611</v>
+        <v>-0.2462884647935877</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.1832150670715119</v>
+        <v>-0.2098618694837724</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.5231978975116587</v>
+        <v>-0.529564063283341</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.2518259395080344</v>
+        <v>-0.2486018626096565</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.5572824876658746</v>
+        <v>-0.5760981456705363</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.1538125871702112</v>
+        <v>-0.1607234013993593</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.4596497902391225</v>
+        <v>-0.4691259825666941</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.3521007330337181</v>
+        <v>0.2521320931753404</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.293584916377472</v>
+        <v>0.210330392399012</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.3991707770672618</v>
+        <v>0.319334341583938</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.2472783033592592</v>
+        <v>0.1174860883103885</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.2633127087586988</v>
+        <v>0.2301307346843615</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.1017247361374281</v>
+        <v>0.05520204768595715</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-15.36539570351063</v>
+        <v>-15.77553506038002</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-0.1055749676951989</v>
+        <v>2.522169224125115</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-23.63975445873264</v>
+        <v>-20.50194391568404</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-30.16672270817882</v>
+        <v>-27.99913008143335</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-19.4106053574377</v>
+        <v>-18.05653282480136</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-14.96840497559581</v>
+        <v>-12.23561927043387</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-30.51726512455907</v>
+        <v>-29.11641077239569</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-20.46555449278062</v>
+        <v>-14.78865447497896</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-39.99528375363252</v>
+        <v>-35.43001586544271</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-46.9634482272441</v>
+        <v>-43.80504132665335</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-31.37545037859966</v>
+        <v>-28.6695418539497</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-28.67872523687764</v>
+        <v>-25.41333652190865</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>2.485998226472469</v>
+        <v>-0.3407674984045393</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>19.13533681618723</v>
+        <v>22.78304782006482</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-7.894192438133723</v>
+        <v>-3.541590863321892</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-9.85742707813221</v>
+        <v>-9.143423430511623</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-8.790402347300647</v>
+        <v>-7.24736048899582</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.7545441843675051</v>
+        <v>0.8757942458111125</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.2930111201953959</v>
+        <v>-0.305726065046428</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.002013266703043328</v>
+        <v>0.04887903131790183</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.4271083408508901</v>
+        <v>-0.3958938681958492</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.5450335326998096</v>
+        <v>-0.5406650198461229</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.360324437588771</v>
+        <v>-0.3493094102264677</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2778626428755793</v>
+        <v>-0.2367019733290284</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.5093217294113144</v>
+        <v>-0.5122755070121805</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.3541018039869313</v>
+        <v>-0.2660436308968865</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.625706460119705</v>
+        <v>-0.600150411748355</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.7745695527517599</v>
+        <v>-0.7864410725139392</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.5213228814162135</v>
+        <v>-0.5103010464567304</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.4899698196756267</v>
+        <v>-0.454958682008457</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.05366692015958996</v>
+        <v>-0.002323138366179038</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.4038412297930039</v>
+        <v>0.5116809095096672</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-0.1729712409058872</v>
+        <v>-0.07459611683586388</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.1939231200337015</v>
+        <v>-0.2153954091075589</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.1741953581614704</v>
+        <v>-0.164480577392574</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.01401669591164808</v>
+        <v>0.0177743249102782</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-7.258712631069958</v>
+        <v>-4.943678484741765</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>4.021558930539326</v>
+        <v>9.471788901335321</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.9921085476183644</v>
+        <v>-0.1989454533636748</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-15.16751954662112</v>
+        <v>-12.11892757543739</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-3.890766586224986</v>
+        <v>-2.546960481399458</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-9.145472292989876</v>
+        <v>-3.553969429596848</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-24.57317368988638</v>
+        <v>-19.86176765112351</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-32.90410044062315</v>
+        <v>-21.66819616773418</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-17.5144446104775</v>
+        <v>-15.04700816787665</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-35.40989407150482</v>
+        <v>-32.24662954048018</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-16.67155981929891</v>
+        <v>-13.30227199397111</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-28.27096014066672</v>
+        <v>-21.36433227735621</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>10.11709585354972</v>
+        <v>9.333746762686612</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>32.1717664670708</v>
+        <v>32.33936916581469</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>16.79757734588973</v>
+        <v>13.9483604899777</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>8.907264684770244</v>
+        <v>10.23640936931988</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>8.361333277213058</v>
+        <v>7.716125503072348</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>11.49453423883069</v>
+        <v>16.59792241971654</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.131374966689098</v>
+        <v>-0.08960133834824144</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.07278593290446472</v>
+        <v>0.1716707437045222</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.0255637293922371</v>
+        <v>-0.005662953210867302</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.3908225225678035</v>
+        <v>-0.3449634996188473</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.08210005401395452</v>
+        <v>-0.05571238892917744</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.192980933859129</v>
+        <v>-0.0777397719949361</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.4066725656988514</v>
+        <v>-0.3368649925398041</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.5639347937419146</v>
+        <v>-0.3590248865572326</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.3975912874020613</v>
+        <v>-0.3786237722398138</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.8359596448612141</v>
+        <v>-0.8115933150407545</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.323161834868089</v>
+        <v>-0.2653851082413218</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.5561289910680871</v>
+        <v>-0.4451334053182703</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.1989449270553562</v>
+        <v>0.1924535443772101</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.6395652553381808</v>
+        <v>0.6519729394672557</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.5205772477566344</v>
+        <v>0.4957846474772173</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.3049742867612306</v>
+        <v>0.3801920100347992</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.2063060960610236</v>
+        <v>0.1946001233228211</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.2676564426277203</v>
+        <v>0.3895140699210929</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-19.48843656697713</v>
+        <v>-10.04955287228477</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-6.359454693424565</v>
+        <v>5.638741715851969</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-20.38021957522496</v>
+        <v>-21.76976492690371</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-5.98166179168243</v>
+        <v>-6.434402755881313</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-19.96087835728038</v>
+        <v>-15.90193172313274</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-6.126484379779257</v>
+        <v>-0.1188449066623742</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-41.17552846397402</v>
+        <v>-29.75875646150399</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-26.95104387080637</v>
+        <v>-13.82930289822431</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-39.93084963343344</v>
+        <v>-38.450101477481</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-27.91334687153354</v>
+        <v>-24.19258639974686</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-35.46283683750744</v>
+        <v>-29.53086183496394</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-21.59181018858922</v>
+        <v>-13.48543722305898</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1.314968074977968</v>
+        <v>8.529051237480369</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>13.96291936304088</v>
+        <v>25.82116044469312</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1.708414888502964</v>
+        <v>-3.332696016100826</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>16.25183890843728</v>
+        <v>15.30174908363401</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-5.452700377242976</v>
+        <v>-3.752488413524943</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>9.513641407849489</v>
+        <v>12.59921992757037</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.3459771883274227</v>
+        <v>-0.2229055093917583</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.1128990643536236</v>
+        <v>0.1250708972303544</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.417613988089944</v>
+        <v>-0.4399088310594675</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.1225710855081485</v>
+        <v>-0.1300221019569893</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.3781610636460426</v>
+        <v>-0.3360648122978754</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.1160669289196474</v>
+        <v>-0.002511618836342297</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.620319285736493</v>
+        <v>-0.5402292802807015</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.4223367366022218</v>
+        <v>-0.2606354281861042</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.6790964823205896</v>
+        <v>-0.6719477212125735</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.4613870049390579</v>
+        <v>-0.4274002544858515</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.5904000568902111</v>
+        <v>-0.5475480226243115</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.3515884423791137</v>
+        <v>-0.260905031419282</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0.02359385381664182</v>
+        <v>0.2652157343431382</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.3053848185114281</v>
+        <v>0.7485284940518439</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.05898948254867638</v>
+        <v>-0.07904962870503694</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.444261611246927</v>
+        <v>0.4176792046441594</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.1280604126436129</v>
+        <v>-0.0889760317472308</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.216775733792627</v>
+        <v>0.31786812290998</v>
       </c>
     </row>
     <row r="34">
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>9.382972704749342</v>
+        <v>6.162056080298478</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>-5.966498403113535</v>
+        <v>-10.707539214446</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-12.85639229201095</v>
+        <v>-17.09768834073558</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-27.69817179791029</v>
+        <v>-25.89974995946311</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-1.543647413272686</v>
+        <v>-5.203432160910793</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>-15.38997642669116</v>
+        <v>-17.28731199553065</v>
       </c>
     </row>
     <row r="35">
@@ -1427,22 +1427,22 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>-6.627469453347621</v>
+        <v>-9.698319108521217</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>-25.65880459779396</v>
+        <v>-29.23697051688873</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-29.08144865075806</v>
+        <v>-33.08431696480014</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-45.73530661502813</v>
+        <v>-42.55118233829635</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-13.81783191387759</v>
+        <v>-18.27942939259436</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-28.00814956346656</v>
+        <v>-31.10608102357549</v>
       </c>
     </row>
     <row r="36">
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>27.83987579227534</v>
+        <v>22.58808673119752</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>12.90707794403349</v>
+        <v>9.576921079401538</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>5.268618496414155</v>
+        <v>-1.503230010831551</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-6.172744635938717</v>
+        <v>-4.879460078071838</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>10.19719812283224</v>
+        <v>5.835442184504555</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>-2.256659681914026</v>
+        <v>-3.352414933885515</v>
       </c>
     </row>
     <row r="37">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.2394692746710468</v>
+        <v>0.1416814337560011</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>-0.1522750933929873</v>
+        <v>-0.2461937197799459</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>-0.2955206794935631</v>
+        <v>-0.365455051010691</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.6366780325717304</v>
+        <v>-0.5535949804423982</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.03728314659990777</v>
+        <v>-0.115365046964482</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.3717084240558315</v>
+        <v>-0.383276172068891</v>
       </c>
     </row>
     <row r="38">
@@ -1505,22 +1505,22 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>-0.1588470075360548</v>
+        <v>-0.1923610567259316</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>-0.5279767883884203</v>
+        <v>-0.58639026750824</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-0.5858109896810433</v>
+        <v>-0.6042097916374343</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.9082277201943918</v>
+        <v>-0.837699583701939</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.2949639402854973</v>
+        <v>-0.3546079867108057</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.6285571377376663</v>
+        <v>-0.6177398514720416</v>
       </c>
     </row>
     <row r="39">
@@ -1531,22 +1531,22 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0.938600181252307</v>
+        <v>0.6942155940617735</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.3787643476718239</v>
+        <v>0.2900269493448672</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.1598518648784082</v>
+        <v>-0.03011292364957101</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.1202341602497226</v>
+        <v>-0.1118968050989225</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.290969427758208</v>
+        <v>0.1568708633264004</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.05722693115541248</v>
+        <v>-0.08529631793611184</v>
       </c>
     </row>
     <row r="40">
@@ -1561,22 +1561,22 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>-23.47835007540503</v>
+        <v>-19.82505431313641</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>-13.14091262951649</v>
+        <v>-12.56217874121854</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-14.39993916858912</v>
+        <v>-14.95433482603803</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-7.300795580714298</v>
+        <v>-5.513816990654647</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-18.69692003473628</v>
+        <v>-17.25380047062811</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>-9.163680046000305</v>
+        <v>-8.494151151441432</v>
       </c>
     </row>
     <row r="41">
@@ -1587,22 +1587,22 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>-34.51745352419006</v>
+        <v>-29.90809714181345</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>-26.16914053866772</v>
+        <v>-24.51765856437958</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-25.1115371856747</v>
+        <v>-25.04275197581693</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-20.11059813235891</v>
+        <v>-17.93829896544775</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-26.69264560847142</v>
+        <v>-24.35179920251876</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>-18.84277303673974</v>
+        <v>-17.71293078649896</v>
       </c>
     </row>
     <row r="42">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>-11.66121699422238</v>
+        <v>-9.301840863986994</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>-0.02707115499956954</v>
+        <v>-0.03364419134687698</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-3.500617273821328</v>
+        <v>-4.860474658154804</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>7.75144360163534</v>
+        <v>8.76766574341676</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-11.07480434794944</v>
+        <v>-9.607644049795136</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>1.200222364597462</v>
+        <v>0.7573830595238454</v>
       </c>
     </row>
     <row r="43">
@@ -1639,22 +1639,22 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>-0.4018885176192429</v>
+        <v>-0.3525079854759395</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>-0.2249383742843465</v>
+        <v>-0.2233672731136669</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-0.3627406539047547</v>
+        <v>-0.3683759833955996</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>-0.1839101771172776</v>
+        <v>-0.1358240122228092</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.3808586154848924</v>
+        <v>-0.355493514320287</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.1866653164575852</v>
+        <v>-0.1750116242003638</v>
       </c>
     </row>
     <row r="44">
@@ -1665,22 +1665,22 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>-0.5512589715841573</v>
+        <v>-0.4960483768452192</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>-0.423585950370077</v>
+        <v>-0.4224120517634578</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-0.5554028292984261</v>
+        <v>-0.558543746580482</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-0.4781000957735848</v>
+        <v>-0.4017029094788299</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.5060228468478275</v>
+        <v>-0.4692250020566421</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.363354410186543</v>
+        <v>-0.3388689471729778</v>
       </c>
     </row>
     <row r="45">
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>-0.2258034529495078</v>
+        <v>-0.1820351747083299</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>-0.000702390328458856</v>
+        <v>-0.00103749947035133</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>-0.0971949973369934</v>
+        <v>-0.142561761505843</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0.2220793100678759</v>
+        <v>0.2480565843784989</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.2373425841311239</v>
+        <v>-0.219519050105566</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.02216434760999419</v>
+        <v>0.02166955745531239</v>
       </c>
     </row>
     <row r="46">
@@ -1721,22 +1721,22 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>-8.659036593514081</v>
+        <v>-5.540416858598479</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>-19.27783592486143</v>
+        <v>-17.40610846146511</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-10.72575976926556</v>
+        <v>-10.03952389561271</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-31.30407579614605</v>
+        <v>-28.12073500717004</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-9.612266409259135</v>
+        <v>-7.546716985689645</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>-23.37896885314708</v>
+        <v>-21.22154955159124</v>
       </c>
     </row>
     <row r="47">
@@ -1747,22 +1747,22 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>-18.06177725602927</v>
+        <v>-14.95656213684708</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>-31.23942496083454</v>
+        <v>-29.93639077124233</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>-20.54979428763267</v>
+        <v>-20.12375847696251</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>-43.28096044363316</v>
+        <v>-38.57258001344278</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-16.39496162383175</v>
+        <v>-14.79938305482751</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>-31.83345667131622</v>
+        <v>-29.57086940689028</v>
       </c>
     </row>
     <row r="48">
@@ -1773,22 +1773,22 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>2.192071509030267</v>
+        <v>4.12440943972222</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>-6.897693223158647</v>
+        <v>-4.868796470302775</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-1.141382737100677</v>
+        <v>-0.488439677316217</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-18.22726456264374</v>
+        <v>-16.83410656202905</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-1.617993098374828</v>
+        <v>-1.457329588636063</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>-14.40037239872196</v>
+        <v>-12.8802039847788</v>
       </c>
     </row>
     <row r="49">
@@ -1799,22 +1799,22 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>-0.1486851998860458</v>
+        <v>-0.09993803669284371</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>-0.3310216854846642</v>
+        <v>-0.3139713762515616</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>-0.2086649591413856</v>
+        <v>-0.2051666854043399</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>-0.6090070855100768</v>
+        <v>-0.5746724697847594</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.1751977712361929</v>
+        <v>-0.144612418847563</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.4261162833487713</v>
+        <v>-0.406653597606533</v>
       </c>
     </row>
     <row r="50">
@@ -1825,22 +1825,22 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>-0.2843622844975951</v>
+        <v>-0.2499319622675243</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>-0.5166024416938779</v>
+        <v>-0.5002259927961641</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-0.361945142000602</v>
+        <v>-0.3780990423863174</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>-0.7790599544468938</v>
+        <v>-0.7561605718734581</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.2866524390280287</v>
+        <v>-0.2646324061703825</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.56064123284957</v>
+        <v>-0.5427621972597544</v>
       </c>
     </row>
     <row r="51">
@@ -1851,22 +1851,22 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>0.04853788255850051</v>
+        <v>0.07685233231420079</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>-0.1230733416126465</v>
+        <v>-0.09081917720663996</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>-0.0209669869722163</v>
+        <v>-0.008500492231605448</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>-0.3758958232440806</v>
+        <v>-0.359477521336922</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.03419929369021579</v>
+        <v>-0.02830554659061465</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.2779017789272884</v>
+        <v>-0.2588957255727377</v>
       </c>
     </row>
     <row r="52">
@@ -1881,22 +1881,22 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>-8.32579242345629</v>
+        <v>-6.958859408935991</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>-12.60069356068003</v>
+        <v>-10.87125575883014</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>-10.25460147098062</v>
+        <v>-10.70933135887874</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>-17.06825775079078</v>
+        <v>-16.06145267180248</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-9.191923394149647</v>
+        <v>-8.677639236170853</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>-14.2007569465679</v>
+        <v>-12.87706306270158</v>
       </c>
     </row>
     <row r="53">
@@ -1907,22 +1907,22 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>-13.25042111320459</v>
+        <v>-11.63589059199919</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>-18.76659200769538</v>
+        <v>-17.00494092666229</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>-15.40815857156266</v>
+        <v>-15.40827692272912</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>-22.84995588658888</v>
+        <v>-21.49067144938049</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-12.73581157673944</v>
+        <v>-11.96284746678382</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>-18.69903729521868</v>
+        <v>-17.17436358614127</v>
       </c>
     </row>
     <row r="54">
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>-3.081794520635174</v>
+        <v>-2.131597794921965</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>-6.635647397371643</v>
+        <v>-4.210654515134935</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>-5.419832303612407</v>
+        <v>-5.954766706598869</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-10.41090064567243</v>
+        <v>-9.142804562176991</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-5.541073835820444</v>
+        <v>-5.416984652203325</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>-9.744870110091576</v>
+        <v>-8.602605151423765</v>
       </c>
     </row>
     <row r="55">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>-0.1550759644441405</v>
+        <v>-0.1339769113739462</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>-0.2347001471094009</v>
+        <v>-0.209301148900059</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>-0.2276652148271062</v>
+        <v>-0.2389945580816009</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>-0.3789370633812267</v>
+        <v>-0.3584350558229324</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.1858428352979701</v>
+        <v>-0.1790609693768958</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.2871117198395308</v>
+        <v>-0.2657150559017968</v>
       </c>
     </row>
     <row r="56">
@@ -1985,22 +1985,22 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>-0.2346496920150425</v>
+        <v>-0.2149353384214662</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>-0.3386070483581766</v>
+        <v>-0.3184251897886948</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>-0.329164891411815</v>
+        <v>-0.3268659071585072</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>-0.4905184027618657</v>
+        <v>-0.4700625846438216</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.2511580052419535</v>
+        <v>-0.2385459607558895</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.3696889872857413</v>
+        <v>-0.3476580540860886</v>
       </c>
     </row>
     <row r="57">
@@ -2011,22 +2011,22 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>-0.06074887369775376</v>
+        <v>-0.04763772599944401</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>-0.1281302121978793</v>
+        <v>-0.08789696238405113</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>-0.1280573769471604</v>
+        <v>-0.1412282835570448</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>-0.2441911100374952</v>
+        <v>-0.212911852004096</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.1172772872610775</v>
+        <v>-0.1139575865841379</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.2013796972570646</v>
+        <v>-0.1850933172479575</v>
       </c>
     </row>
     <row r="58">
